--- a/sheet/8613.xlsx
+++ b/sheet/8613.xlsx
@@ -894,10 +894,10 @@
         <v>9</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>5.78</v>
       </c>
       <c r="H13" t="n">
-        <v>-9</v>
+        <v>-3.22</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1334,10 +1334,10 @@
         <v>9</v>
       </c>
       <c r="G25" t="n">
-        <v>4.47</v>
+        <v>10.57</v>
       </c>
       <c r="H25" t="n">
-        <v>-4.53</v>
+        <v>1.57</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1834,10 +1834,10 @@
         <v>72</v>
       </c>
       <c r="C2" t="n">
-        <v>54.89</v>
+        <v>60.66999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>-17.11</v>
+        <v>-11.33</v>
       </c>
     </row>
     <row r="3">
@@ -1850,10 +1850,10 @@
         <v>72</v>
       </c>
       <c r="C3" t="n">
-        <v>73.06</v>
+        <v>79.16</v>
       </c>
       <c r="D3" t="n">
-        <v>1.06</v>
+        <v>7.16</v>
       </c>
     </row>
     <row r="4">

--- a/sheet/8613.xlsx
+++ b/sheet/8613.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:J61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,7 +470,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>186</v>
+        <v>589</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>187</v>
+        <v>590</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -540,7 +540,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>188</v>
+        <v>591</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>189</v>
+        <v>592</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -594,10 +594,10 @@
         <v>9</v>
       </c>
       <c r="G5" t="n">
-        <v>3.6</v>
+        <v>8.58</v>
       </c>
       <c r="H5" t="n">
-        <v>-5.4</v>
+        <v>-0.42</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -610,7 +610,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>190</v>
+        <v>593</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>191</v>
+        <v>594</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>192</v>
+        <v>595</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>193</v>
+        <v>596</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>194</v>
+        <v>597</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>195</v>
+        <v>598</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>196</v>
+        <v>599</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>197</v>
+        <v>600</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -910,34 +910,34 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>527</v>
+        <v>601</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>KOSTANDY, MICHAEL E [0882]</t>
+          <t>CALINAWAN, MARY JANE BERNARDO [0191]</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>46143</v>
+        <v>46155</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>08:30 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>06:00 PM</t>
+          <t>06:30 PM</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>9</v>
       </c>
       <c r="G14" t="n">
-        <v>9.69</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.13</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -950,24 +950,34 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>528</v>
+        <v>602</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>KOSTANDY, MICHAEL E [0882]</t>
+          <t>CALINAWAN, MARY JANE BERNARDO [0191]</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>46144</v>
+        <v>46156</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -980,24 +990,34 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>529</v>
+        <v>603</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>KOSTANDY, MICHAEL E [0882]</t>
+          <t>CALINAWAN, MARY JANE BERNARDO [0191]</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>46145</v>
+        <v>46157</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1010,34 +1030,24 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>530</v>
+        <v>604</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>KOSTANDY, MICHAEL E [0882]</t>
+          <t>CALINAWAN, MARY JANE BERNARDO [0191]</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>46146</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>08:30 AM</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>06:00 PM</t>
-        </is>
+        <v>46158</v>
       </c>
       <c r="F17" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>9.43</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.43</v>
+        <v>0</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1050,34 +1060,24 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>531</v>
+        <v>605</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>KOSTANDY, MICHAEL E [0882]</t>
+          <t>CALINAWAN, MARY JANE BERNARDO [0191]</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>46147</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>08:30 AM</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>06:00 PM</t>
-        </is>
+        <v>46159</v>
       </c>
       <c r="F18" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>10.72</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1090,34 +1090,34 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>532</v>
+        <v>606</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>KOSTANDY, MICHAEL E [0882]</t>
+          <t>CALINAWAN, MARY JANE BERNARDO [0191]</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>46148</v>
+        <v>46160</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>08:30 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>06:00 PM</t>
+          <t>06:30 PM</t>
         </is>
       </c>
       <c r="F19" t="n">
         <v>9</v>
       </c>
       <c r="G19" t="n">
-        <v>9.550000000000001</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>0.55</v>
+        <v>-0.62</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1130,34 +1130,34 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>533</v>
+        <v>607</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>KOSTANDY, MICHAEL E [0882]</t>
+          <t>CALINAWAN, MARY JANE BERNARDO [0191]</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>46149</v>
+        <v>46161</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>08:30 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>06:00 PM</t>
+          <t>06:30 PM</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>9</v>
       </c>
       <c r="G20" t="n">
-        <v>9.65</v>
+        <v>8.57</v>
       </c>
       <c r="H20" t="n">
-        <v>0.65</v>
+        <v>-0.43</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1170,34 +1170,34 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>534</v>
+        <v>608</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>KOSTANDY, MICHAEL E [0882]</t>
+          <t>CALINAWAN, MARY JANE BERNARDO [0191]</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>46150</v>
+        <v>46162</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>08:30 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>06:00 PM</t>
+          <t>06:30 PM</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>9</v>
       </c>
       <c r="G21" t="n">
-        <v>10.27</v>
+        <v>4.32</v>
       </c>
       <c r="H21" t="n">
-        <v>1.27</v>
+        <v>-4.68</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>535</v>
+        <v>1612</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1218,16 +1218,26 @@
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>46151</v>
+        <v>46143</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>9.69</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1240,7 +1250,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>536</v>
+        <v>1613</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1248,7 +1258,7 @@
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>46152</v>
+        <v>46144</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -1270,7 +1280,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>537</v>
+        <v>1614</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1278,26 +1288,16 @@
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>46153</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>08:30 AM</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>06:00 PM</t>
-        </is>
+        <v>46145</v>
       </c>
       <c r="F24" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>9.279999999999999</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.28</v>
+        <v>0</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>538</v>
+        <v>1615</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>46154</v>
+        <v>46146</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1334,10 +1334,10 @@
         <v>9</v>
       </c>
       <c r="G25" t="n">
-        <v>10.57</v>
+        <v>9.43</v>
       </c>
       <c r="H25" t="n">
-        <v>1.57</v>
+        <v>0.43</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1350,34 +1350,34 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>558</v>
+        <v>1616</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>LA MADRID, EFREN B [0172]</t>
+          <t>KOSTANDY, MICHAEL E [0882]</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>46143</v>
+        <v>46147</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>08:30 AM</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>06:30 PM</t>
+          <t>06:00 PM</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>9</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>10.72</v>
       </c>
       <c r="H26" t="n">
-        <v>-9</v>
+        <v>1.72</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1390,24 +1390,34 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>559</v>
+        <v>1617</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>LA MADRID, EFREN B [0172]</t>
+          <t>KOSTANDY, MICHAEL E [0882]</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>46144</v>
+        <v>46148</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>0.55</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1420,24 +1430,34 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>560</v>
+        <v>1618</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>LA MADRID, EFREN B [0172]</t>
+          <t>KOSTANDY, MICHAEL E [0882]</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>46145</v>
+        <v>46149</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>9.65</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1450,34 +1470,34 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>561</v>
+        <v>1619</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>LA MADRID, EFREN B [0172]</t>
+          <t>KOSTANDY, MICHAEL E [0882]</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>46146</v>
+        <v>46150</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>08:30 AM</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>06:30 PM</t>
+          <t>06:00 PM</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>9</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>10.27</v>
       </c>
       <c r="H29" t="n">
-        <v>-9</v>
+        <v>1.27</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1490,34 +1510,24 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>562</v>
+        <v>1620</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>LA MADRID, EFREN B [0172]</t>
+          <t>KOSTANDY, MICHAEL E [0882]</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>46147</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
+        <v>46151</v>
       </c>
       <c r="F30" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-9</v>
+        <v>0</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1530,34 +1540,24 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>563</v>
+        <v>1621</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>LA MADRID, EFREN B [0172]</t>
+          <t>KOSTANDY, MICHAEL E [0882]</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>46148</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
+        <v>46152</v>
       </c>
       <c r="F31" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-9</v>
+        <v>0</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1570,34 +1570,34 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>564</v>
+        <v>1622</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>LA MADRID, EFREN B [0172]</t>
+          <t>KOSTANDY, MICHAEL E [0882]</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>46149</v>
+        <v>46153</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>08:30 AM</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>06:30 PM</t>
+          <t>06:00 PM</t>
         </is>
       </c>
       <c r="F32" t="n">
         <v>9</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="H32" t="n">
-        <v>-9</v>
+        <v>0.28</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -1610,34 +1610,34 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>565</v>
+        <v>1623</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>LA MADRID, EFREN B [0172]</t>
+          <t>KOSTANDY, MICHAEL E [0882]</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>46150</v>
+        <v>46154</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>08:30 AM</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>06:30 PM</t>
+          <t>06:00 PM</t>
         </is>
       </c>
       <c r="F33" t="n">
         <v>9</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>10.57</v>
       </c>
       <c r="H33" t="n">
-        <v>-9</v>
+        <v>1.57</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -1650,24 +1650,34 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>566</v>
+        <v>1624</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>LA MADRID, EFREN B [0172]</t>
+          <t>KOSTANDY, MICHAEL E [0882]</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>46151</v>
+        <v>46155</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>10.95</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -1680,24 +1690,34 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>567</v>
+        <v>1625</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>LA MADRID, EFREN B [0172]</t>
+          <t>KOSTANDY, MICHAEL E [0882]</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>46152</v>
+        <v>46156</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -1710,34 +1730,34 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>568</v>
+        <v>1626</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>LA MADRID, EFREN B [0172]</t>
+          <t>KOSTANDY, MICHAEL E [0882]</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>46153</v>
+        <v>46157</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>08:30 AM</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>06:30 PM</t>
+          <t>06:00 PM</t>
         </is>
       </c>
       <c r="F36" t="n">
         <v>9</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="H36" t="n">
-        <v>-9</v>
+        <v>0.79</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -1750,41 +1770,891 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>569</v>
+        <v>1627</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
+          <t>KOSTANDY, MICHAEL E [0882]</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Juliet Escalante</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>8613</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>1628</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>KOSTANDY, MICHAEL E [0882]</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Juliet Escalante</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>8613</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>1629</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>KOSTANDY, MICHAEL E [0882]</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>9</v>
+      </c>
+      <c r="G39" t="n">
+        <v>9.16</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Juliet Escalante</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>8613</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>1630</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>KOSTANDY, MICHAEL E [0882]</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>9</v>
+      </c>
+      <c r="G40" t="n">
+        <v>11.07</v>
+      </c>
+      <c r="H40" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Juliet Escalante</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>8613</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>1631</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>KOSTANDY, MICHAEL E [0882]</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>9</v>
+      </c>
+      <c r="G41" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="H41" t="n">
+        <v>-4.62</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Juliet Escalante</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>8613</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>1643</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
           <t>LA MADRID, EFREN B [0172]</t>
         </is>
       </c>
-      <c r="C37" s="2" t="n">
+      <c r="C42" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>9</v>
+      </c>
+      <c r="G42" t="n">
+        <v>9</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Juliet Escalante</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>8613</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>1644</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>LA MADRID, EFREN B [0172]</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Juliet Escalante</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>8613</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>1645</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>LA MADRID, EFREN B [0172]</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Juliet Escalante</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>8613</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>1646</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>LA MADRID, EFREN B [0172]</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="F45" t="n">
+        <v>8</v>
+      </c>
+      <c r="G45" t="n">
+        <v>8</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Juliet Escalante</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>8613</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>1647</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>LA MADRID, EFREN B [0172]</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="F46" t="n">
+        <v>8</v>
+      </c>
+      <c r="G46" t="n">
+        <v>8</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Juliet Escalante</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>8613</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>1648</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>LA MADRID, EFREN B [0172]</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="F47" t="n">
+        <v>8</v>
+      </c>
+      <c r="G47" t="n">
+        <v>8</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Juliet Escalante</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>8613</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>1649</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>LA MADRID, EFREN B [0172]</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>9</v>
+      </c>
+      <c r="G48" t="n">
+        <v>9</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Juliet Escalante</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>8613</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>1650</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>LA MADRID, EFREN B [0172]</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>9</v>
+      </c>
+      <c r="G49" t="n">
+        <v>9</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Juliet Escalante</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>8613</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>1651</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>LA MADRID, EFREN B [0172]</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Juliet Escalante</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>8613</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>1652</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>LA MADRID, EFREN B [0172]</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Juliet Escalante</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>8613</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>1653</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>LA MADRID, EFREN B [0172]</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>9</v>
+      </c>
+      <c r="G52" t="n">
+        <v>9</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Juliet Escalante</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>8613</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>1654</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>LA MADRID, EFREN B [0172]</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="n">
         <v>46154</v>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>09:00 AM</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>06:30 PM</t>
         </is>
       </c>
-      <c r="F37" t="n">
-        <v>9</v>
-      </c>
-      <c r="G37" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" t="n">
+      <c r="F53" t="n">
+        <v>9</v>
+      </c>
+      <c r="G53" t="n">
+        <v>9</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Juliet Escalante</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>8613</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>1655</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>LA MADRID, EFREN B [0172]</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="n">
+        <v>46155</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>9</v>
+      </c>
+      <c r="G54" t="n">
+        <v>9</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Juliet Escalante</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>8613</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>1656</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>LA MADRID, EFREN B [0172]</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>9</v>
+      </c>
+      <c r="G55" t="n">
+        <v>9</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Juliet Escalante</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>8613</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>1657</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>LA MADRID, EFREN B [0172]</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>9</v>
+      </c>
+      <c r="G56" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Juliet Escalante</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>8613</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>1658</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>LA MADRID, EFREN B [0172]</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Juliet Escalante</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>8613</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>1659</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>LA MADRID, EFREN B [0172]</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Juliet Escalante</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>8613</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>1660</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>LA MADRID, EFREN B [0172]</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>9</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="n">
         <v>-9</v>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>Avatco Inc - Juliet Escalante</t>
-        </is>
-      </c>
-      <c r="J37" t="n">
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Juliet Escalante</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>8613</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>1661</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>LA MADRID, EFREN B [0172]</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>9</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="n">
+        <v>-9</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Juliet Escalante</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>8613</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>1662</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>LA MADRID, EFREN B [0172]</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>9</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="n">
+        <v>-9</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Juliet Escalante</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
         <v>8613</v>
       </c>
     </row>
@@ -1831,13 +2701,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>72</v>
+        <v>126</v>
       </c>
       <c r="C2" t="n">
-        <v>60.66999999999999</v>
+        <v>113.75</v>
       </c>
       <c r="D2" t="n">
-        <v>-11.33</v>
+        <v>-12.25</v>
       </c>
     </row>
     <row r="3">
@@ -1847,13 +2717,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>72</v>
+        <v>126</v>
       </c>
       <c r="C3" t="n">
-        <v>79.16</v>
+        <v>133.72</v>
       </c>
       <c r="D3" t="n">
-        <v>7.16</v>
+        <v>7.72</v>
       </c>
     </row>
     <row r="4">
@@ -1863,13 +2733,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>72</v>
+        <v>123</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>96.5</v>
       </c>
       <c r="D4" t="n">
-        <v>-72</v>
+        <v>-26.5</v>
       </c>
     </row>
   </sheetData>

--- a/sheet/8613.xlsx
+++ b/sheet/8613.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J61"/>
+  <dimension ref="A1:J37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,7 +470,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>589</v>
+        <v>186</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>590</v>
+        <v>187</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -540,7 +540,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>591</v>
+        <v>188</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>592</v>
+        <v>189</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -594,10 +594,10 @@
         <v>9</v>
       </c>
       <c r="G5" t="n">
-        <v>8.58</v>
+        <v>3.6</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.42</v>
+        <v>-5.4</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -610,7 +610,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>593</v>
+        <v>190</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>594</v>
+        <v>191</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>595</v>
+        <v>192</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>596</v>
+        <v>193</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>597</v>
+        <v>194</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>598</v>
+        <v>195</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>599</v>
+        <v>196</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>600</v>
+        <v>197</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -910,34 +910,34 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>601</v>
+        <v>527</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CALINAWAN, MARY JANE BERNARDO [0191]</t>
+          <t>KOSTANDY, MICHAEL E [0882]</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>46155</v>
+        <v>46143</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>08:30 AM</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>06:30 PM</t>
+          <t>06:00 PM</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>9</v>
       </c>
       <c r="G14" t="n">
-        <v>9.130000000000001</v>
+        <v>9.69</v>
       </c>
       <c r="H14" t="n">
-        <v>0.13</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -950,34 +950,24 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>602</v>
+        <v>528</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CALINAWAN, MARY JANE BERNARDO [0191]</t>
+          <t>KOSTANDY, MICHAEL E [0882]</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>46156</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
+        <v>46144</v>
       </c>
       <c r="F15" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -990,34 +980,24 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>603</v>
+        <v>529</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CALINAWAN, MARY JANE BERNARDO [0191]</t>
+          <t>KOSTANDY, MICHAEL E [0882]</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>46157</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
+        <v>46145</v>
       </c>
       <c r="F16" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1030,24 +1010,34 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>604</v>
+        <v>530</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CALINAWAN, MARY JANE BERNARDO [0191]</t>
+          <t>KOSTANDY, MICHAEL E [0882]</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>46158</v>
+        <v>46146</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>9.43</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>0.43</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1060,24 +1050,34 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>605</v>
+        <v>531</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CALINAWAN, MARY JANE BERNARDO [0191]</t>
+          <t>KOSTANDY, MICHAEL E [0882]</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>46159</v>
+        <v>46147</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>10.72</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1090,34 +1090,34 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>606</v>
+        <v>532</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CALINAWAN, MARY JANE BERNARDO [0191]</t>
+          <t>KOSTANDY, MICHAEL E [0882]</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>46160</v>
+        <v>46148</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>08:30 AM</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>06:30 PM</t>
+          <t>06:00 PM</t>
         </is>
       </c>
       <c r="F19" t="n">
         <v>9</v>
       </c>
       <c r="G19" t="n">
-        <v>8.380000000000001</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.62</v>
+        <v>0.55</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1130,34 +1130,34 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>607</v>
+        <v>533</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CALINAWAN, MARY JANE BERNARDO [0191]</t>
+          <t>KOSTANDY, MICHAEL E [0882]</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>46161</v>
+        <v>46149</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>08:30 AM</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>06:30 PM</t>
+          <t>06:00 PM</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>9</v>
       </c>
       <c r="G20" t="n">
-        <v>8.57</v>
+        <v>9.65</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.43</v>
+        <v>0.65</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1170,34 +1170,34 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>608</v>
+        <v>534</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CALINAWAN, MARY JANE BERNARDO [0191]</t>
+          <t>KOSTANDY, MICHAEL E [0882]</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>46162</v>
+        <v>46150</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>08:30 AM</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>06:30 PM</t>
+          <t>06:00 PM</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>9</v>
       </c>
       <c r="G21" t="n">
-        <v>4.32</v>
+        <v>10.27</v>
       </c>
       <c r="H21" t="n">
-        <v>-4.68</v>
+        <v>1.27</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1612</v>
+        <v>535</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1218,26 +1218,16 @@
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>46143</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>08:30 AM</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>06:00 PM</t>
-        </is>
+        <v>46151</v>
       </c>
       <c r="F22" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>9.69</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.6899999999999999</v>
+        <v>0</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1250,7 +1240,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1613</v>
+        <v>536</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1258,7 +1248,7 @@
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>46144</v>
+        <v>46152</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -1280,7 +1270,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1614</v>
+        <v>537</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1288,16 +1278,26 @@
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>46145</v>
+        <v>46153</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>0.28</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1615</v>
+        <v>538</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>46146</v>
+        <v>46154</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1334,10 +1334,10 @@
         <v>9</v>
       </c>
       <c r="G25" t="n">
-        <v>9.43</v>
+        <v>10.57</v>
       </c>
       <c r="H25" t="n">
-        <v>0.43</v>
+        <v>1.57</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1350,34 +1350,34 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1616</v>
+        <v>558</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>KOSTANDY, MICHAEL E [0882]</t>
+          <t>LA MADRID, EFREN B [0172]</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>46147</v>
+        <v>46143</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>08:30 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>06:00 PM</t>
+          <t>06:30 PM</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>9</v>
       </c>
       <c r="G26" t="n">
-        <v>10.72</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1.72</v>
+        <v>-9</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1390,34 +1390,24 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1617</v>
+        <v>559</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>KOSTANDY, MICHAEL E [0882]</t>
+          <t>LA MADRID, EFREN B [0172]</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>46148</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>08:30 AM</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>06:00 PM</t>
-        </is>
+        <v>46144</v>
       </c>
       <c r="F27" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>9.550000000000001</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.55</v>
+        <v>0</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1430,34 +1420,24 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1618</v>
+        <v>560</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>KOSTANDY, MICHAEL E [0882]</t>
+          <t>LA MADRID, EFREN B [0172]</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>46149</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>08:30 AM</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>06:00 PM</t>
-        </is>
+        <v>46145</v>
       </c>
       <c r="F28" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>9.65</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.65</v>
+        <v>0</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1470,34 +1450,34 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1619</v>
+        <v>561</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>KOSTANDY, MICHAEL E [0882]</t>
+          <t>LA MADRID, EFREN B [0172]</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>46150</v>
+        <v>46146</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>08:30 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>06:00 PM</t>
+          <t>06:30 PM</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>9</v>
       </c>
       <c r="G29" t="n">
-        <v>10.27</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1.27</v>
+        <v>-9</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1510,24 +1490,34 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1620</v>
+        <v>562</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>KOSTANDY, MICHAEL E [0882]</t>
+          <t>LA MADRID, EFREN B [0172]</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>46151</v>
+        <v>46147</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1540,24 +1530,34 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1621</v>
+        <v>563</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>KOSTANDY, MICHAEL E [0882]</t>
+          <t>LA MADRID, EFREN B [0172]</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>46152</v>
+        <v>46148</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1570,34 +1570,34 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>1622</v>
+        <v>564</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>KOSTANDY, MICHAEL E [0882]</t>
+          <t>LA MADRID, EFREN B [0172]</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>46153</v>
+        <v>46149</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>08:30 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>06:00 PM</t>
+          <t>06:30 PM</t>
         </is>
       </c>
       <c r="F32" t="n">
         <v>9</v>
       </c>
       <c r="G32" t="n">
-        <v>9.279999999999999</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.28</v>
+        <v>-9</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -1610,34 +1610,34 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>1623</v>
+        <v>565</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>KOSTANDY, MICHAEL E [0882]</t>
+          <t>LA MADRID, EFREN B [0172]</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>46154</v>
+        <v>46150</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>08:30 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>06:00 PM</t>
+          <t>06:30 PM</t>
         </is>
       </c>
       <c r="F33" t="n">
         <v>9</v>
       </c>
       <c r="G33" t="n">
-        <v>10.57</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>1.57</v>
+        <v>-9</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -1650,34 +1650,24 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>1624</v>
+        <v>566</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>KOSTANDY, MICHAEL E [0882]</t>
+          <t>LA MADRID, EFREN B [0172]</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>46155</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>08:30 AM</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>06:00 PM</t>
-        </is>
+        <v>46151</v>
       </c>
       <c r="F34" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>10.95</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -1690,34 +1680,24 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>1625</v>
+        <v>567</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>KOSTANDY, MICHAEL E [0882]</t>
+          <t>LA MADRID, EFREN B [0172]</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>46156</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>08:30 AM</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>06:00 PM</t>
-        </is>
+        <v>46152</v>
       </c>
       <c r="F35" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>9.210000000000001</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0.21</v>
+        <v>0</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -1730,34 +1710,34 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>1626</v>
+        <v>568</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>KOSTANDY, MICHAEL E [0882]</t>
+          <t>LA MADRID, EFREN B [0172]</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>46157</v>
+        <v>46153</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>08:30 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>06:00 PM</t>
+          <t>06:30 PM</t>
         </is>
       </c>
       <c r="F36" t="n">
         <v>9</v>
       </c>
       <c r="G36" t="n">
-        <v>9.789999999999999</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.79</v>
+        <v>-9</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -1770,24 +1750,34 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>1627</v>
+        <v>569</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>KOSTANDY, MICHAEL E [0882]</t>
+          <t>LA MADRID, EFREN B [0172]</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>46158</v>
+        <v>46154</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -1795,866 +1785,6 @@
         </is>
       </c>
       <c r="J37" t="n">
-        <v>8613</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>1628</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>KOSTANDY, MICHAEL E [0882]</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="n">
-        <v>46159</v>
-      </c>
-      <c r="F38" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>Avatco Inc - Juliet Escalante</t>
-        </is>
-      </c>
-      <c r="J38" t="n">
-        <v>8613</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>1629</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>KOSTANDY, MICHAEL E [0882]</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="n">
-        <v>46160</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>08:30 AM</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>06:00 PM</t>
-        </is>
-      </c>
-      <c r="F39" t="n">
-        <v>9</v>
-      </c>
-      <c r="G39" t="n">
-        <v>9.16</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>Avatco Inc - Juliet Escalante</t>
-        </is>
-      </c>
-      <c r="J39" t="n">
-        <v>8613</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>1630</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>KOSTANDY, MICHAEL E [0882]</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="n">
-        <v>46161</v>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>08:30 AM</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>06:00 PM</t>
-        </is>
-      </c>
-      <c r="F40" t="n">
-        <v>9</v>
-      </c>
-      <c r="G40" t="n">
-        <v>11.07</v>
-      </c>
-      <c r="H40" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>Avatco Inc - Juliet Escalante</t>
-        </is>
-      </c>
-      <c r="J40" t="n">
-        <v>8613</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>1631</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>KOSTANDY, MICHAEL E [0882]</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="n">
-        <v>46162</v>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>08:30 AM</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>06:00 PM</t>
-        </is>
-      </c>
-      <c r="F41" t="n">
-        <v>9</v>
-      </c>
-      <c r="G41" t="n">
-        <v>4.38</v>
-      </c>
-      <c r="H41" t="n">
-        <v>-4.62</v>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>Avatco Inc - Juliet Escalante</t>
-        </is>
-      </c>
-      <c r="J41" t="n">
-        <v>8613</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>1643</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>LA MADRID, EFREN B [0172]</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="n">
-        <v>46143</v>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
-      </c>
-      <c r="F42" t="n">
-        <v>9</v>
-      </c>
-      <c r="G42" t="n">
-        <v>9</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>Avatco Inc - Juliet Escalante</t>
-        </is>
-      </c>
-      <c r="J42" t="n">
-        <v>8613</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>1644</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>LA MADRID, EFREN B [0172]</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="n">
-        <v>46144</v>
-      </c>
-      <c r="F43" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>Avatco Inc - Juliet Escalante</t>
-        </is>
-      </c>
-      <c r="J43" t="n">
-        <v>8613</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>1645</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>LA MADRID, EFREN B [0172]</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="n">
-        <v>46145</v>
-      </c>
-      <c r="F44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>Avatco Inc - Juliet Escalante</t>
-        </is>
-      </c>
-      <c r="J44" t="n">
-        <v>8613</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>1646</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>LA MADRID, EFREN B [0172]</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="n">
-        <v>46146</v>
-      </c>
-      <c r="F45" t="n">
-        <v>8</v>
-      </c>
-      <c r="G45" t="n">
-        <v>8</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>Avatco Inc - Juliet Escalante</t>
-        </is>
-      </c>
-      <c r="J45" t="n">
-        <v>8613</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>1647</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>LA MADRID, EFREN B [0172]</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="n">
-        <v>46147</v>
-      </c>
-      <c r="F46" t="n">
-        <v>8</v>
-      </c>
-      <c r="G46" t="n">
-        <v>8</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>Avatco Inc - Juliet Escalante</t>
-        </is>
-      </c>
-      <c r="J46" t="n">
-        <v>8613</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>1648</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>LA MADRID, EFREN B [0172]</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="n">
-        <v>46148</v>
-      </c>
-      <c r="F47" t="n">
-        <v>8</v>
-      </c>
-      <c r="G47" t="n">
-        <v>8</v>
-      </c>
-      <c r="H47" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>Avatco Inc - Juliet Escalante</t>
-        </is>
-      </c>
-      <c r="J47" t="n">
-        <v>8613</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>1649</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>LA MADRID, EFREN B [0172]</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="n">
-        <v>46149</v>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
-      </c>
-      <c r="F48" t="n">
-        <v>9</v>
-      </c>
-      <c r="G48" t="n">
-        <v>9</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>Avatco Inc - Juliet Escalante</t>
-        </is>
-      </c>
-      <c r="J48" t="n">
-        <v>8613</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>1650</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>LA MADRID, EFREN B [0172]</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="n">
-        <v>46150</v>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
-      </c>
-      <c r="F49" t="n">
-        <v>9</v>
-      </c>
-      <c r="G49" t="n">
-        <v>9</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>Avatco Inc - Juliet Escalante</t>
-        </is>
-      </c>
-      <c r="J49" t="n">
-        <v>8613</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>1651</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>LA MADRID, EFREN B [0172]</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="n">
-        <v>46151</v>
-      </c>
-      <c r="F50" t="n">
-        <v>0</v>
-      </c>
-      <c r="G50" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>Avatco Inc - Juliet Escalante</t>
-        </is>
-      </c>
-      <c r="J50" t="n">
-        <v>8613</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>1652</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>LA MADRID, EFREN B [0172]</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="n">
-        <v>46152</v>
-      </c>
-      <c r="F51" t="n">
-        <v>0</v>
-      </c>
-      <c r="G51" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>Avatco Inc - Juliet Escalante</t>
-        </is>
-      </c>
-      <c r="J51" t="n">
-        <v>8613</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>1653</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>LA MADRID, EFREN B [0172]</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="n">
-        <v>46153</v>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
-      </c>
-      <c r="F52" t="n">
-        <v>9</v>
-      </c>
-      <c r="G52" t="n">
-        <v>9</v>
-      </c>
-      <c r="H52" t="n">
-        <v>0</v>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>Avatco Inc - Juliet Escalante</t>
-        </is>
-      </c>
-      <c r="J52" t="n">
-        <v>8613</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>1654</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>LA MADRID, EFREN B [0172]</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="n">
-        <v>46154</v>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
-      </c>
-      <c r="F53" t="n">
-        <v>9</v>
-      </c>
-      <c r="G53" t="n">
-        <v>9</v>
-      </c>
-      <c r="H53" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>Avatco Inc - Juliet Escalante</t>
-        </is>
-      </c>
-      <c r="J53" t="n">
-        <v>8613</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>1655</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>LA MADRID, EFREN B [0172]</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="n">
-        <v>46155</v>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
-      </c>
-      <c r="F54" t="n">
-        <v>9</v>
-      </c>
-      <c r="G54" t="n">
-        <v>9</v>
-      </c>
-      <c r="H54" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>Avatco Inc - Juliet Escalante</t>
-        </is>
-      </c>
-      <c r="J54" t="n">
-        <v>8613</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>1656</v>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>LA MADRID, EFREN B [0172]</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="n">
-        <v>46156</v>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
-      </c>
-      <c r="F55" t="n">
-        <v>9</v>
-      </c>
-      <c r="G55" t="n">
-        <v>9</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0</v>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>Avatco Inc - Juliet Escalante</t>
-        </is>
-      </c>
-      <c r="J55" t="n">
-        <v>8613</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>1657</v>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>LA MADRID, EFREN B [0172]</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="n">
-        <v>46157</v>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
-      </c>
-      <c r="F56" t="n">
-        <v>9</v>
-      </c>
-      <c r="G56" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="H56" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>Avatco Inc - Juliet Escalante</t>
-        </is>
-      </c>
-      <c r="J56" t="n">
-        <v>8613</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>1658</v>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>LA MADRID, EFREN B [0172]</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="n">
-        <v>46158</v>
-      </c>
-      <c r="F57" t="n">
-        <v>0</v>
-      </c>
-      <c r="G57" t="n">
-        <v>0</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>Avatco Inc - Juliet Escalante</t>
-        </is>
-      </c>
-      <c r="J57" t="n">
-        <v>8613</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>1659</v>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>LA MADRID, EFREN B [0172]</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="n">
-        <v>46159</v>
-      </c>
-      <c r="F58" t="n">
-        <v>0</v>
-      </c>
-      <c r="G58" t="n">
-        <v>0</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>Avatco Inc - Juliet Escalante</t>
-        </is>
-      </c>
-      <c r="J58" t="n">
-        <v>8613</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>1660</v>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>LA MADRID, EFREN B [0172]</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="n">
-        <v>46160</v>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
-      </c>
-      <c r="F59" t="n">
-        <v>9</v>
-      </c>
-      <c r="G59" t="n">
-        <v>0</v>
-      </c>
-      <c r="H59" t="n">
-        <v>-9</v>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>Avatco Inc - Juliet Escalante</t>
-        </is>
-      </c>
-      <c r="J59" t="n">
-        <v>8613</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="n">
-        <v>1661</v>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>LA MADRID, EFREN B [0172]</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="n">
-        <v>46161</v>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
-      </c>
-      <c r="F60" t="n">
-        <v>9</v>
-      </c>
-      <c r="G60" t="n">
-        <v>0</v>
-      </c>
-      <c r="H60" t="n">
-        <v>-9</v>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>Avatco Inc - Juliet Escalante</t>
-        </is>
-      </c>
-      <c r="J60" t="n">
-        <v>8613</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
-        <v>1662</v>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>LA MADRID, EFREN B [0172]</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="n">
-        <v>46162</v>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
-      </c>
-      <c r="F61" t="n">
-        <v>9</v>
-      </c>
-      <c r="G61" t="n">
-        <v>0</v>
-      </c>
-      <c r="H61" t="n">
-        <v>-9</v>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>Avatco Inc - Juliet Escalante</t>
-        </is>
-      </c>
-      <c r="J61" t="n">
         <v>8613</v>
       </c>
     </row>
@@ -2701,13 +1831,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>126</v>
+        <v>72</v>
       </c>
       <c r="C2" t="n">
-        <v>113.75</v>
+        <v>60.66999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>-12.25</v>
+        <v>-11.33</v>
       </c>
     </row>
     <row r="3">
@@ -2717,13 +1847,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>126</v>
+        <v>72</v>
       </c>
       <c r="C3" t="n">
-        <v>133.72</v>
+        <v>79.16</v>
       </c>
       <c r="D3" t="n">
-        <v>7.72</v>
+        <v>7.16</v>
       </c>
     </row>
     <row r="4">
@@ -2733,13 +1863,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>123</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>96.5</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-26.5</v>
+        <v>-72</v>
       </c>
     </row>
   </sheetData>

--- a/sheet/8613.xlsx
+++ b/sheet/8613.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:J61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,7 +470,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>186</v>
+        <v>589</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>187</v>
+        <v>590</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -540,7 +540,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>188</v>
+        <v>591</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>189</v>
+        <v>592</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -594,10 +594,10 @@
         <v>9</v>
       </c>
       <c r="G5" t="n">
-        <v>3.6</v>
+        <v>8.58</v>
       </c>
       <c r="H5" t="n">
-        <v>-5.4</v>
+        <v>-0.42</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -610,7 +610,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>190</v>
+        <v>593</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>191</v>
+        <v>594</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>192</v>
+        <v>595</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>193</v>
+        <v>596</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>194</v>
+        <v>597</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>195</v>
+        <v>598</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>196</v>
+        <v>599</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>197</v>
+        <v>600</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -910,34 +910,34 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>527</v>
+        <v>601</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>KOSTANDY, MICHAEL E [0882]</t>
+          <t>CALINAWAN, MARY JANE BERNARDO [0191]</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>46143</v>
+        <v>46155</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>08:30 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>06:00 PM</t>
+          <t>06:30 PM</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>9</v>
       </c>
       <c r="G14" t="n">
-        <v>9.69</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.13</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -950,24 +950,34 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>528</v>
+        <v>602</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>KOSTANDY, MICHAEL E [0882]</t>
+          <t>CALINAWAN, MARY JANE BERNARDO [0191]</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>46144</v>
+        <v>46156</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -980,24 +990,34 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>529</v>
+        <v>603</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>KOSTANDY, MICHAEL E [0882]</t>
+          <t>CALINAWAN, MARY JANE BERNARDO [0191]</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>46145</v>
+        <v>46157</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1010,34 +1030,24 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>530</v>
+        <v>604</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>KOSTANDY, MICHAEL E [0882]</t>
+          <t>CALINAWAN, MARY JANE BERNARDO [0191]</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>46146</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>08:30 AM</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>06:00 PM</t>
-        </is>
+        <v>46158</v>
       </c>
       <c r="F17" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>9.43</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.43</v>
+        <v>0</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1050,34 +1060,24 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>531</v>
+        <v>605</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>KOSTANDY, MICHAEL E [0882]</t>
+          <t>CALINAWAN, MARY JANE BERNARDO [0191]</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>46147</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>08:30 AM</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>06:00 PM</t>
-        </is>
+        <v>46159</v>
       </c>
       <c r="F18" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>10.72</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1090,34 +1090,34 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>532</v>
+        <v>606</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>KOSTANDY, MICHAEL E [0882]</t>
+          <t>CALINAWAN, MARY JANE BERNARDO [0191]</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>46148</v>
+        <v>46160</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>08:30 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>06:00 PM</t>
+          <t>06:30 PM</t>
         </is>
       </c>
       <c r="F19" t="n">
         <v>9</v>
       </c>
       <c r="G19" t="n">
-        <v>9.550000000000001</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>0.55</v>
+        <v>-0.62</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1130,34 +1130,34 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>533</v>
+        <v>607</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>KOSTANDY, MICHAEL E [0882]</t>
+          <t>CALINAWAN, MARY JANE BERNARDO [0191]</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>46149</v>
+        <v>46161</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>08:30 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>06:00 PM</t>
+          <t>06:30 PM</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>9</v>
       </c>
       <c r="G20" t="n">
-        <v>9.65</v>
+        <v>8.57</v>
       </c>
       <c r="H20" t="n">
-        <v>0.65</v>
+        <v>-0.43</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1170,34 +1170,34 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>534</v>
+        <v>608</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>KOSTANDY, MICHAEL E [0882]</t>
+          <t>CALINAWAN, MARY JANE BERNARDO [0191]</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>46150</v>
+        <v>46162</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>08:30 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>06:00 PM</t>
+          <t>06:30 PM</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>9</v>
       </c>
       <c r="G21" t="n">
-        <v>10.27</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>1.27</v>
+        <v>-0.03</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>535</v>
+        <v>1612</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1218,16 +1218,26 @@
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>46151</v>
+        <v>46143</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>9.69</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1240,7 +1250,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>536</v>
+        <v>1613</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1248,7 +1258,7 @@
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>46152</v>
+        <v>46144</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -1270,7 +1280,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>537</v>
+        <v>1614</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1278,26 +1288,16 @@
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>46153</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>08:30 AM</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>06:00 PM</t>
-        </is>
+        <v>46145</v>
       </c>
       <c r="F24" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>9.279999999999999</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.28</v>
+        <v>0</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>538</v>
+        <v>1615</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>46154</v>
+        <v>46146</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1334,10 +1334,10 @@
         <v>9</v>
       </c>
       <c r="G25" t="n">
-        <v>10.57</v>
+        <v>9.43</v>
       </c>
       <c r="H25" t="n">
-        <v>1.57</v>
+        <v>0.43</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1350,34 +1350,34 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>558</v>
+        <v>1616</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>LA MADRID, EFREN B [0172]</t>
+          <t>KOSTANDY, MICHAEL E [0882]</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>46143</v>
+        <v>46147</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>08:30 AM</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>06:30 PM</t>
+          <t>06:00 PM</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>9</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>10.72</v>
       </c>
       <c r="H26" t="n">
-        <v>-9</v>
+        <v>1.72</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1390,24 +1390,34 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>559</v>
+        <v>1617</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>LA MADRID, EFREN B [0172]</t>
+          <t>KOSTANDY, MICHAEL E [0882]</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>46144</v>
+        <v>46148</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>0.55</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1420,24 +1430,34 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>560</v>
+        <v>1618</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>LA MADRID, EFREN B [0172]</t>
+          <t>KOSTANDY, MICHAEL E [0882]</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>46145</v>
+        <v>46149</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>9.65</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1450,34 +1470,34 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>561</v>
+        <v>1619</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>LA MADRID, EFREN B [0172]</t>
+          <t>KOSTANDY, MICHAEL E [0882]</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>46146</v>
+        <v>46150</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>08:30 AM</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>06:30 PM</t>
+          <t>06:00 PM</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>9</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>10.27</v>
       </c>
       <c r="H29" t="n">
-        <v>-9</v>
+        <v>1.27</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1490,34 +1510,24 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>562</v>
+        <v>1620</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>LA MADRID, EFREN B [0172]</t>
+          <t>KOSTANDY, MICHAEL E [0882]</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>46147</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
+        <v>46151</v>
       </c>
       <c r="F30" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-9</v>
+        <v>0</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1530,34 +1540,24 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>563</v>
+        <v>1621</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>LA MADRID, EFREN B [0172]</t>
+          <t>KOSTANDY, MICHAEL E [0882]</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>46148</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
+        <v>46152</v>
       </c>
       <c r="F31" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-9</v>
+        <v>0</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1570,34 +1570,34 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>564</v>
+        <v>1622</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>LA MADRID, EFREN B [0172]</t>
+          <t>KOSTANDY, MICHAEL E [0882]</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>46149</v>
+        <v>46153</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>08:30 AM</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>06:30 PM</t>
+          <t>06:00 PM</t>
         </is>
       </c>
       <c r="F32" t="n">
         <v>9</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="H32" t="n">
-        <v>-9</v>
+        <v>0.28</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -1610,34 +1610,34 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>565</v>
+        <v>1623</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>LA MADRID, EFREN B [0172]</t>
+          <t>KOSTANDY, MICHAEL E [0882]</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>46150</v>
+        <v>46154</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>08:30 AM</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>06:30 PM</t>
+          <t>06:00 PM</t>
         </is>
       </c>
       <c r="F33" t="n">
         <v>9</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>10.57</v>
       </c>
       <c r="H33" t="n">
-        <v>-9</v>
+        <v>1.57</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -1650,24 +1650,34 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>566</v>
+        <v>1624</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>LA MADRID, EFREN B [0172]</t>
+          <t>KOSTANDY, MICHAEL E [0882]</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>46151</v>
+        <v>46155</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>10.95</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -1680,24 +1690,34 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>567</v>
+        <v>1625</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>LA MADRID, EFREN B [0172]</t>
+          <t>KOSTANDY, MICHAEL E [0882]</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>46152</v>
+        <v>46156</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -1710,34 +1730,34 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>568</v>
+        <v>1626</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>LA MADRID, EFREN B [0172]</t>
+          <t>KOSTANDY, MICHAEL E [0882]</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>46153</v>
+        <v>46157</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>08:30 AM</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>06:30 PM</t>
+          <t>06:00 PM</t>
         </is>
       </c>
       <c r="F36" t="n">
         <v>9</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="H36" t="n">
-        <v>-9</v>
+        <v>0.79</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -1750,41 +1770,891 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>569</v>
+        <v>1627</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
+          <t>KOSTANDY, MICHAEL E [0882]</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Juliet Escalante</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>8613</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>1628</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>KOSTANDY, MICHAEL E [0882]</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Juliet Escalante</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>8613</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>1629</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>KOSTANDY, MICHAEL E [0882]</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>9</v>
+      </c>
+      <c r="G39" t="n">
+        <v>9.16</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Juliet Escalante</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>8613</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>1630</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>KOSTANDY, MICHAEL E [0882]</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>9</v>
+      </c>
+      <c r="G40" t="n">
+        <v>11.07</v>
+      </c>
+      <c r="H40" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Juliet Escalante</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>8613</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>1631</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>KOSTANDY, MICHAEL E [0882]</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>9</v>
+      </c>
+      <c r="G41" t="n">
+        <v>9.68</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Juliet Escalante</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>8613</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>1643</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
           <t>LA MADRID, EFREN B [0172]</t>
         </is>
       </c>
-      <c r="C37" s="2" t="n">
+      <c r="C42" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>9</v>
+      </c>
+      <c r="G42" t="n">
+        <v>9</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Juliet Escalante</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>8613</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>1644</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>LA MADRID, EFREN B [0172]</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Juliet Escalante</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>8613</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>1645</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>LA MADRID, EFREN B [0172]</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Juliet Escalante</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>8613</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>1646</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>LA MADRID, EFREN B [0172]</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="F45" t="n">
+        <v>8</v>
+      </c>
+      <c r="G45" t="n">
+        <v>8</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Juliet Escalante</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>8613</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>1647</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>LA MADRID, EFREN B [0172]</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="F46" t="n">
+        <v>8</v>
+      </c>
+      <c r="G46" t="n">
+        <v>8</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Juliet Escalante</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>8613</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>1648</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>LA MADRID, EFREN B [0172]</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="F47" t="n">
+        <v>8</v>
+      </c>
+      <c r="G47" t="n">
+        <v>8</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Juliet Escalante</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>8613</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>1649</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>LA MADRID, EFREN B [0172]</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>9</v>
+      </c>
+      <c r="G48" t="n">
+        <v>9</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Juliet Escalante</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>8613</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>1650</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>LA MADRID, EFREN B [0172]</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>9</v>
+      </c>
+      <c r="G49" t="n">
+        <v>9</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Juliet Escalante</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>8613</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>1651</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>LA MADRID, EFREN B [0172]</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Juliet Escalante</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>8613</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>1652</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>LA MADRID, EFREN B [0172]</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Juliet Escalante</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>8613</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>1653</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>LA MADRID, EFREN B [0172]</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>9</v>
+      </c>
+      <c r="G52" t="n">
+        <v>9</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Juliet Escalante</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>8613</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>1654</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>LA MADRID, EFREN B [0172]</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="n">
         <v>46154</v>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>09:00 AM</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>06:30 PM</t>
         </is>
       </c>
-      <c r="F37" t="n">
-        <v>9</v>
-      </c>
-      <c r="G37" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" t="n">
-        <v>-9</v>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>Avatco Inc - Juliet Escalante</t>
-        </is>
-      </c>
-      <c r="J37" t="n">
+      <c r="F53" t="n">
+        <v>9</v>
+      </c>
+      <c r="G53" t="n">
+        <v>9</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Juliet Escalante</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>8613</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>1655</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>LA MADRID, EFREN B [0172]</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="n">
+        <v>46155</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>9</v>
+      </c>
+      <c r="G54" t="n">
+        <v>9</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Juliet Escalante</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>8613</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>1656</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>LA MADRID, EFREN B [0172]</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>9</v>
+      </c>
+      <c r="G55" t="n">
+        <v>9</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Juliet Escalante</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>8613</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>1657</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>LA MADRID, EFREN B [0172]</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>9</v>
+      </c>
+      <c r="G56" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Juliet Escalante</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>8613</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>1658</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>LA MADRID, EFREN B [0172]</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Juliet Escalante</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>8613</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>1659</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>LA MADRID, EFREN B [0172]</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Juliet Escalante</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>8613</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>1660</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>LA MADRID, EFREN B [0172]</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>9</v>
+      </c>
+      <c r="G59" t="n">
+        <v>9</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Juliet Escalante</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>8613</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>1661</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>LA MADRID, EFREN B [0172]</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>9</v>
+      </c>
+      <c r="G60" t="n">
+        <v>9</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Juliet Escalante</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>8613</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>1662</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>LA MADRID, EFREN B [0172]</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>9</v>
+      </c>
+      <c r="G61" t="n">
+        <v>9</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Juliet Escalante</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
         <v>8613</v>
       </c>
     </row>
@@ -1831,13 +2701,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>72</v>
+        <v>126</v>
       </c>
       <c r="C2" t="n">
-        <v>60.66999999999999</v>
+        <v>118.4</v>
       </c>
       <c r="D2" t="n">
-        <v>-11.33</v>
+        <v>-7.600000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -1847,13 +2717,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>72</v>
+        <v>126</v>
       </c>
       <c r="C3" t="n">
-        <v>79.16</v>
+        <v>139.02</v>
       </c>
       <c r="D3" t="n">
-        <v>7.16</v>
+        <v>13.02</v>
       </c>
     </row>
     <row r="4">
@@ -1863,13 +2733,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>72</v>
+        <v>123</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>123.5</v>
       </c>
       <c r="D4" t="n">
-        <v>-72</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>

--- a/sheet/8613.xlsx
+++ b/sheet/8613.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J61"/>
+  <dimension ref="A1:J64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1210,34 +1210,34 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1612</v>
+        <v>609</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>KOSTANDY, MICHAEL E [0882]</t>
+          <t>CALINAWAN, MARY JANE BERNARDO [0191]</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>46143</v>
+        <v>46163</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>08:30 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>06:00 PM</t>
+          <t>06:30 PM</t>
         </is>
       </c>
       <c r="F22" t="n">
         <v>9</v>
       </c>
       <c r="G22" t="n">
-        <v>9.69</v>
+        <v>4.38</v>
       </c>
       <c r="H22" t="n">
-        <v>0.6899999999999999</v>
+        <v>-4.62</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1258,16 +1258,26 @@
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>46144</v>
+        <v>46143</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>9.69</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1280,7 +1290,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1288,7 +1298,7 @@
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>46145</v>
+        <v>46144</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -1310,7 +1320,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1615</v>
+        <v>1614</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -1318,26 +1328,16 @@
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>46146</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>08:30 AM</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>06:00 PM</t>
-        </is>
+        <v>46145</v>
       </c>
       <c r="F25" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>9.43</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.43</v>
+        <v>0</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1616</v>
+        <v>1615</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>46147</v>
+        <v>46146</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1374,10 +1374,10 @@
         <v>9</v>
       </c>
       <c r="G26" t="n">
-        <v>10.72</v>
+        <v>9.43</v>
       </c>
       <c r="H26" t="n">
-        <v>1.72</v>
+        <v>0.43</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>46148</v>
+        <v>46147</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1414,10 +1414,10 @@
         <v>9</v>
       </c>
       <c r="G27" t="n">
-        <v>9.550000000000001</v>
+        <v>10.72</v>
       </c>
       <c r="H27" t="n">
-        <v>0.55</v>
+        <v>1.72</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>46149</v>
+        <v>46148</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1454,10 +1454,10 @@
         <v>9</v>
       </c>
       <c r="G28" t="n">
-        <v>9.65</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="H28" t="n">
-        <v>0.65</v>
+        <v>0.55</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>46150</v>
+        <v>46149</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1494,10 +1494,10 @@
         <v>9</v>
       </c>
       <c r="G29" t="n">
-        <v>10.27</v>
+        <v>9.65</v>
       </c>
       <c r="H29" t="n">
-        <v>1.27</v>
+        <v>0.65</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -1518,16 +1518,26 @@
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>46151</v>
+        <v>46150</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>10.27</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1540,7 +1550,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -1548,7 +1558,7 @@
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>46152</v>
+        <v>46151</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -1570,7 +1580,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -1578,26 +1588,16 @@
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>46153</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>08:30 AM</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>06:00 PM</t>
-        </is>
+        <v>46152</v>
       </c>
       <c r="F32" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>9.279999999999999</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.28</v>
+        <v>0</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>46154</v>
+        <v>46153</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1634,10 +1634,10 @@
         <v>9</v>
       </c>
       <c r="G33" t="n">
-        <v>10.57</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="H33" t="n">
-        <v>1.57</v>
+        <v>0.28</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>46155</v>
+        <v>46154</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1674,10 +1674,10 @@
         <v>9</v>
       </c>
       <c r="G34" t="n">
-        <v>10.95</v>
+        <v>10.57</v>
       </c>
       <c r="H34" t="n">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>46156</v>
+        <v>46155</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1714,10 +1714,10 @@
         <v>9</v>
       </c>
       <c r="G35" t="n">
-        <v>9.210000000000001</v>
+        <v>10.95</v>
       </c>
       <c r="H35" t="n">
-        <v>0.21</v>
+        <v>1.95</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>46157</v>
+        <v>46156</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1754,10 +1754,10 @@
         <v>9</v>
       </c>
       <c r="G36" t="n">
-        <v>9.789999999999999</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="H36" t="n">
-        <v>0.79</v>
+        <v>0.21</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -1778,16 +1778,26 @@
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>46158</v>
+        <v>46157</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>0.79</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -1800,7 +1810,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -1808,7 +1818,7 @@
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>46159</v>
+        <v>46158</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -1830,7 +1840,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -1838,26 +1848,16 @@
         </is>
       </c>
       <c r="C39" s="2" t="n">
-        <v>46160</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>08:30 AM</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>06:00 PM</t>
-        </is>
+        <v>46159</v>
       </c>
       <c r="F39" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>9.16</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>46161</v>
+        <v>46160</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -1894,10 +1894,10 @@
         <v>9</v>
       </c>
       <c r="G40" t="n">
-        <v>11.07</v>
+        <v>9.16</v>
       </c>
       <c r="H40" t="n">
-        <v>2.07</v>
+        <v>0.16</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>46162</v>
+        <v>46161</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -1934,10 +1934,10 @@
         <v>9</v>
       </c>
       <c r="G41" t="n">
-        <v>9.68</v>
+        <v>11.07</v>
       </c>
       <c r="H41" t="n">
-        <v>0.68</v>
+        <v>2.07</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -1950,34 +1950,34 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>1643</v>
+        <v>1631</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>LA MADRID, EFREN B [0172]</t>
+          <t>KOSTANDY, MICHAEL E [0882]</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
-        <v>46143</v>
+        <v>46162</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>08:30 AM</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>06:30 PM</t>
+          <t>06:00 PM</t>
         </is>
       </c>
       <c r="F42" t="n">
         <v>9</v>
       </c>
       <c r="G42" t="n">
-        <v>9</v>
+        <v>9.68</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>0.68</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -1990,24 +1990,34 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>1644</v>
+        <v>1632</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>LA MADRID, EFREN B [0172]</t>
+          <t>KOSTANDY, MICHAEL E [0882]</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>46144</v>
+        <v>46163</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>-4.92</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2020,7 +2030,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>1645</v>
+        <v>1643</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -2028,13 +2038,23 @@
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>46145</v>
+        <v>46143</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -2050,7 +2070,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>1646</v>
+        <v>1644</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -2058,13 +2078,13 @@
         </is>
       </c>
       <c r="C45" s="2" t="n">
-        <v>46146</v>
+        <v>46144</v>
       </c>
       <c r="F45" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -2080,7 +2100,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>1647</v>
+        <v>1645</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -2088,13 +2108,13 @@
         </is>
       </c>
       <c r="C46" s="2" t="n">
-        <v>46147</v>
+        <v>46145</v>
       </c>
       <c r="F46" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
@@ -2110,7 +2130,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>1648</v>
+        <v>1646</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -2118,7 +2138,7 @@
         </is>
       </c>
       <c r="C47" s="2" t="n">
-        <v>46148</v>
+        <v>46146</v>
       </c>
       <c r="F47" t="n">
         <v>8</v>
@@ -2140,7 +2160,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>1649</v>
+        <v>1647</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -2148,23 +2168,13 @@
         </is>
       </c>
       <c r="C48" s="2" t="n">
-        <v>46149</v>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
+        <v>46147</v>
       </c>
       <c r="F48" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G48" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
@@ -2180,7 +2190,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>1650</v>
+        <v>1648</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -2188,23 +2198,13 @@
         </is>
       </c>
       <c r="C49" s="2" t="n">
-        <v>46150</v>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
+        <v>46148</v>
       </c>
       <c r="F49" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G49" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
@@ -2220,7 +2220,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>1651</v>
+        <v>1649</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -2228,13 +2228,23 @@
         </is>
       </c>
       <c r="C50" s="2" t="n">
-        <v>46151</v>
+        <v>46149</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
@@ -2250,7 +2260,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>1652</v>
+        <v>1650</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -2258,13 +2268,23 @@
         </is>
       </c>
       <c r="C51" s="2" t="n">
-        <v>46152</v>
+        <v>46150</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
@@ -2280,7 +2300,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>1653</v>
+        <v>1651</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -2288,23 +2308,13 @@
         </is>
       </c>
       <c r="C52" s="2" t="n">
-        <v>46153</v>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
+        <v>46151</v>
       </c>
       <c r="F52" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G52" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
@@ -2320,7 +2330,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>1654</v>
+        <v>1652</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -2328,23 +2338,13 @@
         </is>
       </c>
       <c r="C53" s="2" t="n">
-        <v>46154</v>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
+        <v>46152</v>
       </c>
       <c r="F53" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -2360,7 +2360,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>1655</v>
+        <v>1653</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         </is>
       </c>
       <c r="C54" s="2" t="n">
-        <v>46155</v>
+        <v>46153</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -2400,7 +2400,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>1656</v>
+        <v>1654</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -2408,7 +2408,7 @@
         </is>
       </c>
       <c r="C55" s="2" t="n">
-        <v>46156</v>
+        <v>46154</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>1657</v>
+        <v>1655</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         </is>
       </c>
       <c r="C56" s="2" t="n">
-        <v>46157</v>
+        <v>46155</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -2464,10 +2464,10 @@
         <v>9</v>
       </c>
       <c r="G56" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="H56" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>1658</v>
+        <v>1656</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -2488,13 +2488,23 @@
         </is>
       </c>
       <c r="C57" s="2" t="n">
-        <v>46158</v>
+        <v>46156</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -2510,7 +2520,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>1659</v>
+        <v>1657</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -2518,16 +2528,26 @@
         </is>
       </c>
       <c r="C58" s="2" t="n">
-        <v>46159</v>
+        <v>46157</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
       </c>
       <c r="F58" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -2540,7 +2560,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>1660</v>
+        <v>1658</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -2548,23 +2568,13 @@
         </is>
       </c>
       <c r="C59" s="2" t="n">
-        <v>46160</v>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
+        <v>46158</v>
       </c>
       <c r="F59" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -2580,7 +2590,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>1661</v>
+        <v>1659</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -2588,23 +2598,13 @@
         </is>
       </c>
       <c r="C60" s="2" t="n">
-        <v>46161</v>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
+        <v>46159</v>
       </c>
       <c r="F60" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
@@ -2620,41 +2620,161 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
+        <v>1660</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>LA MADRID, EFREN B [0172]</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>9</v>
+      </c>
+      <c r="G61" t="n">
+        <v>9</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Juliet Escalante</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>8613</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>1661</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>LA MADRID, EFREN B [0172]</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>9</v>
+      </c>
+      <c r="G62" t="n">
+        <v>9</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Juliet Escalante</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>8613</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
         <v>1662</v>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>LA MADRID, EFREN B [0172]</t>
         </is>
       </c>
-      <c r="C61" s="2" t="n">
+      <c r="C63" s="2" t="n">
         <v>46162</v>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>09:00 AM</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>06:30 PM</t>
         </is>
       </c>
-      <c r="F61" t="n">
-        <v>9</v>
-      </c>
-      <c r="G61" t="n">
-        <v>9</v>
-      </c>
-      <c r="H61" t="n">
-        <v>0</v>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>Avatco Inc - Juliet Escalante</t>
-        </is>
-      </c>
-      <c r="J61" t="n">
+      <c r="F63" t="n">
+        <v>9</v>
+      </c>
+      <c r="G63" t="n">
+        <v>9</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Juliet Escalante</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>8613</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>1663</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>LA MADRID, EFREN B [0172]</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>9</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
+        <v>-9</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Juliet Escalante</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
         <v>8613</v>
       </c>
     </row>
@@ -2701,13 +2821,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="C2" t="n">
-        <v>118.4</v>
+        <v>122.78</v>
       </c>
       <c r="D2" t="n">
-        <v>-7.600000000000001</v>
+        <v>-12.22</v>
       </c>
     </row>
     <row r="3">
@@ -2717,13 +2837,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="C3" t="n">
-        <v>139.02</v>
+        <v>143.1</v>
       </c>
       <c r="D3" t="n">
-        <v>13.02</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="4">
@@ -2733,13 +2853,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="C4" t="n">
         <v>123.5</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5</v>
+        <v>-8.5</v>
       </c>
     </row>
   </sheetData>

--- a/sheet/8613.xlsx
+++ b/sheet/8613.xlsx
@@ -1234,10 +1234,10 @@
         <v>9</v>
       </c>
       <c r="G22" t="n">
-        <v>4.38</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>-4.62</v>
+        <v>-0.39</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2014,10 +2014,10 @@
         <v>9</v>
       </c>
       <c r="G43" t="n">
-        <v>4.08</v>
+        <v>9.23</v>
       </c>
       <c r="H43" t="n">
-        <v>-4.92</v>
+        <v>0.23</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         <v>135</v>
       </c>
       <c r="C2" t="n">
-        <v>122.78</v>
+        <v>127.01</v>
       </c>
       <c r="D2" t="n">
-        <v>-12.22</v>
+        <v>-7.99</v>
       </c>
     </row>
     <row r="3">
@@ -2840,10 +2840,10 @@
         <v>135</v>
       </c>
       <c r="C3" t="n">
-        <v>143.1</v>
+        <v>148.25</v>
       </c>
       <c r="D3" t="n">
-        <v>8.1</v>
+        <v>13.25</v>
       </c>
     </row>
     <row r="4">

--- a/sheet/8613.xlsx
+++ b/sheet/8613.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J64"/>
+  <dimension ref="A1:J85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1250,34 +1250,34 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1612</v>
+        <v>610</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>KOSTANDY, MICHAEL E [0882]</t>
+          <t>CALINAWAN, MARY JANE BERNARDO [0191]</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>46143</v>
+        <v>46164</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>08:30 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>06:00 PM</t>
+          <t>06:30 PM</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>9</v>
       </c>
       <c r="G23" t="n">
-        <v>9.69</v>
+        <v>8.5</v>
       </c>
       <c r="H23" t="n">
-        <v>0.6899999999999999</v>
+        <v>-0.5</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1290,15 +1290,15 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1613</v>
+        <v>611</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>KOSTANDY, MICHAEL E [0882]</t>
+          <t>CALINAWAN, MARY JANE BERNARDO [0191]</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>46144</v>
+        <v>46165</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -1320,15 +1320,15 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1614</v>
+        <v>612</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>KOSTANDY, MICHAEL E [0882]</t>
+          <t>CALINAWAN, MARY JANE BERNARDO [0191]</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>46145</v>
+        <v>46166</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -1350,34 +1350,34 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1615</v>
+        <v>613</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>KOSTANDY, MICHAEL E [0882]</t>
+          <t>CALINAWAN, MARY JANE BERNARDO [0191]</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>46146</v>
+        <v>46167</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>08:30 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>06:00 PM</t>
+          <t>06:30 PM</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>9</v>
       </c>
       <c r="G26" t="n">
-        <v>9.43</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.43</v>
+        <v>-9</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1390,34 +1390,34 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1616</v>
+        <v>614</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>KOSTANDY, MICHAEL E [0882]</t>
+          <t>CALINAWAN, MARY JANE BERNARDO [0191]</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>46147</v>
+        <v>46168</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>08:30 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>06:00 PM</t>
+          <t>06:30 PM</t>
         </is>
       </c>
       <c r="F27" t="n">
         <v>9</v>
       </c>
       <c r="G27" t="n">
-        <v>10.72</v>
+        <v>4.5</v>
       </c>
       <c r="H27" t="n">
-        <v>1.72</v>
+        <v>-4.5</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1430,34 +1430,34 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1617</v>
+        <v>615</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>KOSTANDY, MICHAEL E [0882]</t>
+          <t>CALINAWAN, MARY JANE BERNARDO [0191]</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>46148</v>
+        <v>46169</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>08:30 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>06:00 PM</t>
+          <t>06:30 PM</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>9</v>
       </c>
       <c r="G28" t="n">
-        <v>9.550000000000001</v>
+        <v>8.75</v>
       </c>
       <c r="H28" t="n">
-        <v>0.55</v>
+        <v>-0.25</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1470,34 +1470,34 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1618</v>
+        <v>616</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>KOSTANDY, MICHAEL E [0882]</t>
+          <t>CALINAWAN, MARY JANE BERNARDO [0191]</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>46149</v>
+        <v>46170</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>08:30 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>06:00 PM</t>
+          <t>06:30 PM</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>9</v>
       </c>
       <c r="G29" t="n">
-        <v>9.65</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.65</v>
+        <v>-9</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1619</v>
+        <v>1581</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>46150</v>
+        <v>46143</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1534,10 +1534,10 @@
         <v>9</v>
       </c>
       <c r="G30" t="n">
-        <v>10.27</v>
+        <v>9.69</v>
       </c>
       <c r="H30" t="n">
-        <v>1.27</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1620</v>
+        <v>1582</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>46151</v>
+        <v>46144</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -1580,7 +1580,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>1621</v>
+        <v>1583</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>46152</v>
+        <v>46145</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
@@ -1610,7 +1610,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>1622</v>
+        <v>1584</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>46153</v>
+        <v>46146</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1634,10 +1634,10 @@
         <v>9</v>
       </c>
       <c r="G33" t="n">
-        <v>9.279999999999999</v>
+        <v>9.43</v>
       </c>
       <c r="H33" t="n">
-        <v>0.28</v>
+        <v>0.43</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>1623</v>
+        <v>1585</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>46154</v>
+        <v>46147</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1674,10 +1674,10 @@
         <v>9</v>
       </c>
       <c r="G34" t="n">
-        <v>10.57</v>
+        <v>10.72</v>
       </c>
       <c r="H34" t="n">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>1624</v>
+        <v>1586</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>46155</v>
+        <v>46148</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1714,10 +1714,10 @@
         <v>9</v>
       </c>
       <c r="G35" t="n">
-        <v>10.95</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="H35" t="n">
-        <v>1.95</v>
+        <v>0.55</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>1625</v>
+        <v>1587</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>46156</v>
+        <v>46149</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1754,10 +1754,10 @@
         <v>9</v>
       </c>
       <c r="G36" t="n">
-        <v>9.210000000000001</v>
+        <v>9.65</v>
       </c>
       <c r="H36" t="n">
-        <v>0.21</v>
+        <v>0.65</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>1626</v>
+        <v>1588</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>46157</v>
+        <v>46150</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1794,10 +1794,10 @@
         <v>9</v>
       </c>
       <c r="G37" t="n">
-        <v>9.789999999999999</v>
+        <v>10.27</v>
       </c>
       <c r="H37" t="n">
-        <v>0.79</v>
+        <v>1.27</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1627</v>
+        <v>1589</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>46158</v>
+        <v>46151</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -1840,7 +1840,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>1628</v>
+        <v>1590</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         </is>
       </c>
       <c r="C39" s="2" t="n">
-        <v>46159</v>
+        <v>46152</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -1870,7 +1870,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>1629</v>
+        <v>1591</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>46160</v>
+        <v>46153</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -1894,10 +1894,10 @@
         <v>9</v>
       </c>
       <c r="G40" t="n">
-        <v>9.16</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="H40" t="n">
-        <v>0.16</v>
+        <v>0.28</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>1630</v>
+        <v>1592</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>46161</v>
+        <v>46154</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -1934,10 +1934,10 @@
         <v>9</v>
       </c>
       <c r="G41" t="n">
-        <v>11.07</v>
+        <v>10.57</v>
       </c>
       <c r="H41" t="n">
-        <v>2.07</v>
+        <v>1.57</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -1950,7 +1950,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>1631</v>
+        <v>1593</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         </is>
       </c>
       <c r="C42" s="2" t="n">
-        <v>46162</v>
+        <v>46155</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -1974,10 +1974,10 @@
         <v>9</v>
       </c>
       <c r="G42" t="n">
-        <v>9.68</v>
+        <v>10.95</v>
       </c>
       <c r="H42" t="n">
-        <v>0.68</v>
+        <v>1.95</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>1632</v>
+        <v>1594</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>46163</v>
+        <v>46156</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -2014,10 +2014,10 @@
         <v>9</v>
       </c>
       <c r="G43" t="n">
-        <v>9.23</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="H43" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2030,34 +2030,34 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>1643</v>
+        <v>1595</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>LA MADRID, EFREN B [0172]</t>
+          <t>KOSTANDY, MICHAEL E [0882]</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>46143</v>
+        <v>46157</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>08:30 AM</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>06:30 PM</t>
+          <t>06:00 PM</t>
         </is>
       </c>
       <c r="F44" t="n">
         <v>9</v>
       </c>
       <c r="G44" t="n">
-        <v>9</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>0.79</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2070,15 +2070,15 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>1644</v>
+        <v>1596</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>LA MADRID, EFREN B [0172]</t>
+          <t>KOSTANDY, MICHAEL E [0882]</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
-        <v>46144</v>
+        <v>46158</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -2100,15 +2100,15 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>1645</v>
+        <v>1597</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>LA MADRID, EFREN B [0172]</t>
+          <t>KOSTANDY, MICHAEL E [0882]</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
-        <v>46145</v>
+        <v>46159</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
@@ -2130,24 +2130,34 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>1646</v>
+        <v>1598</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>LA MADRID, EFREN B [0172]</t>
+          <t>KOSTANDY, MICHAEL E [0882]</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
-        <v>46146</v>
+        <v>46160</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
       </c>
       <c r="F47" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G47" t="n">
-        <v>8</v>
+        <v>9.16</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2160,24 +2170,34 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>1647</v>
+        <v>1599</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>LA MADRID, EFREN B [0172]</t>
+          <t>KOSTANDY, MICHAEL E [0882]</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
-        <v>46147</v>
+        <v>46161</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
       </c>
       <c r="F48" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G48" t="n">
-        <v>8</v>
+        <v>11.07</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2190,24 +2210,34 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>1648</v>
+        <v>1600</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>LA MADRID, EFREN B [0172]</t>
+          <t>KOSTANDY, MICHAEL E [0882]</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
-        <v>46148</v>
+        <v>46162</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
       </c>
       <c r="F49" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G49" t="n">
-        <v>8</v>
+        <v>9.68</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>0.68</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -2220,34 +2250,34 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>1649</v>
+        <v>1601</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>LA MADRID, EFREN B [0172]</t>
+          <t>KOSTANDY, MICHAEL E [0882]</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
-        <v>46149</v>
+        <v>46163</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>08:30 AM</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>06:30 PM</t>
+          <t>06:00 PM</t>
         </is>
       </c>
       <c r="F50" t="n">
         <v>9</v>
       </c>
       <c r="G50" t="n">
-        <v>9</v>
+        <v>9.23</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -2260,34 +2290,34 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>1650</v>
+        <v>1602</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>LA MADRID, EFREN B [0172]</t>
+          <t>KOSTANDY, MICHAEL E [0882]</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
-        <v>46150</v>
+        <v>46164</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>08:30 AM</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>06:30 PM</t>
+          <t>06:00 PM</t>
         </is>
       </c>
       <c r="F51" t="n">
         <v>9</v>
       </c>
       <c r="G51" t="n">
-        <v>9</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -2300,15 +2330,15 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>1651</v>
+        <v>1603</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>LA MADRID, EFREN B [0172]</t>
+          <t>KOSTANDY, MICHAEL E [0882]</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
-        <v>46151</v>
+        <v>46165</v>
       </c>
       <c r="F52" t="n">
         <v>0</v>
@@ -2330,15 +2360,15 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>1652</v>
+        <v>1604</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>LA MADRID, EFREN B [0172]</t>
+          <t>KOSTANDY, MICHAEL E [0882]</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
-        <v>46152</v>
+        <v>46166</v>
       </c>
       <c r="F53" t="n">
         <v>0</v>
@@ -2360,34 +2390,34 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>1653</v>
+        <v>1605</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>LA MADRID, EFREN B [0172]</t>
+          <t>KOSTANDY, MICHAEL E [0882]</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
-        <v>46153</v>
+        <v>46167</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>08:30 AM</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>06:30 PM</t>
+          <t>06:00 PM</t>
         </is>
       </c>
       <c r="F54" t="n">
         <v>9</v>
       </c>
       <c r="G54" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -2400,34 +2430,34 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>1654</v>
+        <v>1606</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>LA MADRID, EFREN B [0172]</t>
+          <t>KOSTANDY, MICHAEL E [0882]</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
-        <v>46154</v>
+        <v>46168</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>08:30 AM</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>06:30 PM</t>
+          <t>06:00 PM</t>
         </is>
       </c>
       <c r="F55" t="n">
         <v>9</v>
       </c>
       <c r="G55" t="n">
-        <v>9</v>
+        <v>10.27</v>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -2440,34 +2470,34 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>1655</v>
+        <v>1607</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>LA MADRID, EFREN B [0172]</t>
+          <t>KOSTANDY, MICHAEL E [0882]</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
-        <v>46155</v>
+        <v>46169</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>08:30 AM</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>06:30 PM</t>
+          <t>06:00 PM</t>
         </is>
       </c>
       <c r="F56" t="n">
         <v>9</v>
       </c>
       <c r="G56" t="n">
-        <v>9</v>
+        <v>9.75</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -2480,34 +2510,34 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>1656</v>
+        <v>1608</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>LA MADRID, EFREN B [0172]</t>
+          <t>KOSTANDY, MICHAEL E [0882]</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
-        <v>46156</v>
+        <v>46170</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>08:30 AM</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>06:30 PM</t>
+          <t>06:00 PM</t>
         </is>
       </c>
       <c r="F57" t="n">
         <v>9</v>
       </c>
       <c r="G57" t="n">
-        <v>9</v>
+        <v>4.37</v>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>-4.63</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -2520,7 +2550,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>1657</v>
+        <v>1612</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -2528,7 +2558,7 @@
         </is>
       </c>
       <c r="C58" s="2" t="n">
-        <v>46157</v>
+        <v>46143</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -2544,10 +2574,10 @@
         <v>9</v>
       </c>
       <c r="G58" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="H58" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -2560,7 +2590,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>1658</v>
+        <v>1613</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -2568,7 +2598,7 @@
         </is>
       </c>
       <c r="C59" s="2" t="n">
-        <v>46158</v>
+        <v>46144</v>
       </c>
       <c r="F59" t="n">
         <v>0</v>
@@ -2590,7 +2620,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>1659</v>
+        <v>1614</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -2598,7 +2628,7 @@
         </is>
       </c>
       <c r="C60" s="2" t="n">
-        <v>46159</v>
+        <v>46145</v>
       </c>
       <c r="F60" t="n">
         <v>0</v>
@@ -2620,7 +2650,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>1660</v>
+        <v>1615</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -2628,23 +2658,13 @@
         </is>
       </c>
       <c r="C61" s="2" t="n">
-        <v>46160</v>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
+        <v>46146</v>
       </c>
       <c r="F61" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G61" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
@@ -2660,7 +2680,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>1661</v>
+        <v>1616</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -2668,23 +2688,13 @@
         </is>
       </c>
       <c r="C62" s="2" t="n">
-        <v>46161</v>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
+        <v>46147</v>
       </c>
       <c r="F62" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G62" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
@@ -2700,7 +2710,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>1662</v>
+        <v>1617</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -2708,23 +2718,13 @@
         </is>
       </c>
       <c r="C63" s="2" t="n">
-        <v>46162</v>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
+        <v>46148</v>
       </c>
       <c r="F63" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G63" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -2740,7 +2740,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>1663</v>
+        <v>1618</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -2748,33 +2748,813 @@
         </is>
       </c>
       <c r="C64" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>9</v>
+      </c>
+      <c r="G64" t="n">
+        <v>9</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Juliet Escalante</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>8613</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>1619</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>LA MADRID, EFREN B [0172]</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>9</v>
+      </c>
+      <c r="G65" t="n">
+        <v>9</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Juliet Escalante</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>8613</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>1620</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>LA MADRID, EFREN B [0172]</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Juliet Escalante</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>8613</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>1621</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>LA MADRID, EFREN B [0172]</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Juliet Escalante</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>8613</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>1622</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>LA MADRID, EFREN B [0172]</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>9</v>
+      </c>
+      <c r="G68" t="n">
+        <v>9</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Juliet Escalante</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>8613</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>1623</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>LA MADRID, EFREN B [0172]</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>9</v>
+      </c>
+      <c r="G69" t="n">
+        <v>9</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Juliet Escalante</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>8613</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>1624</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>LA MADRID, EFREN B [0172]</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v>46155</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>9</v>
+      </c>
+      <c r="G70" t="n">
+        <v>9</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Juliet Escalante</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>8613</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>1625</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>LA MADRID, EFREN B [0172]</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>9</v>
+      </c>
+      <c r="G71" t="n">
+        <v>9</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Juliet Escalante</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>8613</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>1626</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>LA MADRID, EFREN B [0172]</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>9</v>
+      </c>
+      <c r="G72" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Juliet Escalante</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>8613</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>1627</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>LA MADRID, EFREN B [0172]</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Juliet Escalante</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>8613</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>1628</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>LA MADRID, EFREN B [0172]</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Juliet Escalante</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>8613</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>1629</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>LA MADRID, EFREN B [0172]</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>9</v>
+      </c>
+      <c r="G75" t="n">
+        <v>9</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Juliet Escalante</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>8613</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>1630</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>LA MADRID, EFREN B [0172]</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>9</v>
+      </c>
+      <c r="G76" t="n">
+        <v>9</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Juliet Escalante</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>8613</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>1631</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>LA MADRID, EFREN B [0172]</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>9</v>
+      </c>
+      <c r="G77" t="n">
+        <v>9</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Juliet Escalante</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
+        <v>8613</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>1632</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>LA MADRID, EFREN B [0172]</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="n">
         <v>46163</v>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="D78" t="inlineStr">
         <is>
           <t>09:00 AM</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="E78" t="inlineStr">
         <is>
           <t>06:30 PM</t>
         </is>
       </c>
-      <c r="F64" t="n">
-        <v>9</v>
-      </c>
-      <c r="G64" t="n">
-        <v>0</v>
-      </c>
-      <c r="H64" t="n">
+      <c r="F78" t="n">
+        <v>9</v>
+      </c>
+      <c r="G78" t="n">
+        <v>9.68</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Juliet Escalante</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>8613</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>1633</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>LA MADRID, EFREN B [0172]</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>9</v>
+      </c>
+      <c r="G79" t="n">
+        <v>9.57</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Juliet Escalante</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
+        <v>8613</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>1634</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>LA MADRID, EFREN B [0172]</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Juliet Escalante</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>8613</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>1635</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>LA MADRID, EFREN B [0172]</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Juliet Escalante</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
+        <v>8613</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>1636</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>LA MADRID, EFREN B [0172]</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="n">
+        <v>46167</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>9</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" t="n">
         <v>-9</v>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>Avatco Inc - Juliet Escalante</t>
-        </is>
-      </c>
-      <c r="J64" t="n">
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Juliet Escalante</t>
+        </is>
+      </c>
+      <c r="J82" t="n">
+        <v>8613</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>1637</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>LA MADRID, EFREN B [0172]</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="n">
+        <v>46168</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>9</v>
+      </c>
+      <c r="G83" t="n">
+        <v>9.17</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Juliet Escalante</t>
+        </is>
+      </c>
+      <c r="J83" t="n">
+        <v>8613</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>1638</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>LA MADRID, EFREN B [0172]</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="n">
+        <v>46169</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>9</v>
+      </c>
+      <c r="G84" t="n">
+        <v>9.07</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Juliet Escalante</t>
+        </is>
+      </c>
+      <c r="J84" t="n">
+        <v>8613</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>1639</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>LA MADRID, EFREN B [0172]</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="n">
+        <v>46170</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>9</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" t="n">
+        <v>-9</v>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Juliet Escalante</t>
+        </is>
+      </c>
+      <c r="J85" t="n">
         <v>8613</v>
       </c>
     </row>
@@ -2821,13 +3601,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="C2" t="n">
-        <v>127.01</v>
+        <v>148.76</v>
       </c>
       <c r="D2" t="n">
-        <v>-7.99</v>
+        <v>-31.24</v>
       </c>
     </row>
     <row r="3">
@@ -2837,13 +3617,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="C3" t="n">
-        <v>148.25</v>
+        <v>182.09</v>
       </c>
       <c r="D3" t="n">
-        <v>13.25</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="4">
@@ -2853,13 +3633,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>132</v>
+        <v>177</v>
       </c>
       <c r="C4" t="n">
-        <v>123.5</v>
+        <v>160.99</v>
       </c>
       <c r="D4" t="n">
-        <v>-8.5</v>
+        <v>-16.01</v>
       </c>
     </row>
   </sheetData>

--- a/sheet/8613.xlsx
+++ b/sheet/8613.xlsx
@@ -1494,10 +1494,10 @@
         <v>9</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="H29" t="n">
-        <v>-9</v>
+        <v>0.37</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -3604,10 +3604,10 @@
         <v>180</v>
       </c>
       <c r="C2" t="n">
-        <v>148.76</v>
+        <v>158.13</v>
       </c>
       <c r="D2" t="n">
-        <v>-31.24</v>
+        <v>-21.87</v>
       </c>
     </row>
     <row r="3">
